--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.2</v>
+        <v>55.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>37.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.7</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>37.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1451,24 +1443,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -1476,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1486,12 +1478,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,26 +1506,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>37.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -1541,14 +1533,14 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>2</t>
@@ -1566,12 +1558,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1593,27 +1585,27 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1623,102 +1615,102 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1769,12 +1761,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1794,7 +1786,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1832,11 +1824,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>47.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -1845,13 +1837,13 @@
         <v>37.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>13.3</v>
+        <v>65.2</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -1859,39 +1851,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1911,22 +1899,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1936,72 +1924,72 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2036,7 +2024,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2087,12 +2075,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2102,7 +2090,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2112,12 +2100,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2136,7 +2124,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,11 +2138,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="n">
         <v>18.6</v>
@@ -2163,31 +2151,33 @@
         <v>37.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V6" t="n">
-        <v>50</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>48</v>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2202,12 +2192,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2229,12 +2219,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2244,82 +2234,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2354,7 +2344,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2388,16 +2378,56 @@
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2405,24 +2435,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -2430,7 +2460,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,12 +2470,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2454,7 +2484,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,68 +2498,62 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>62</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>37.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
+        <v>80</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="V7" t="n">
         <v>50</v>
       </c>
-      <c r="U7" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>48</v>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2549,7 +2573,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2564,117 +2588,117 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2708,56 +2732,16 @@
         </is>
       </c>
       <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2765,12 +2749,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2790,12 +2774,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2814,7 +2798,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>47.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,11 +2812,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
@@ -2841,13 +2825,13 @@
         <v>37.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2855,39 +2839,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2907,7 +2887,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2917,87 +2897,87 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3032,7 +3012,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3083,12 +3063,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,12 +3088,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3132,7 +3112,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,11 +3126,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
@@ -3159,13 +3139,13 @@
         <v>37.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3173,39 +3153,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3225,7 +3201,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3240,12 +3216,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -3255,67 +3231,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -3350,7 +3326,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3406,7 +3382,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3426,12 +3402,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3450,7 +3426,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>43.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3440,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3453,7 @@
         <v>37.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3491,14 +3467,14 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>6</t>
@@ -3516,12 +3492,12 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3668,7 +3644,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3724,7 +3700,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3744,7 +3720,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3744,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3758,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3771,7 @@
         <v>37.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3809,14 +3785,14 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>1</t>
@@ -3834,12 +3810,12 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -3986,7 +3962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4062,12 +4038,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,7 +4076,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -4113,7 +4089,7 @@
         <v>37.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -4127,14 +4103,14 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>4</t>
@@ -4152,12 +4128,12 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -4304,7 +4280,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,24 +4331,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -4380,22 +4356,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4404,7 +4380,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,26 +4394,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>37.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,17 +4421,17 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4470,17 +4446,17 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -4497,7 +4473,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4507,17 +4483,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,102 +4503,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4674,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4698,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4712,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4725,7 @@
         <v>37.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4763,39 +4739,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -4940,7 +4912,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4963,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5016,7 +4988,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5040,7 +5012,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>32.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,11 +5026,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
@@ -5067,13 +5039,13 @@
         <v>37.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5053,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,12 +5101,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,12 +5116,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,27 +5131,27 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -5193,37 +5161,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5226,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,12 +5277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5334,12 +5302,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5358,7 +5326,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>32.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,11 +5340,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
@@ -5385,13 +5353,13 @@
         <v>37.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>70.59999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,17 +5367,17 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5424,12 +5392,12 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -5451,27 +5419,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,67 +5449,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5576,7 +5544,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,24 +5595,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -5652,7 +5620,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5662,12 +5630,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5676,7 +5644,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5658,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
         <v>37.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,39 +5685,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5769,12 +5733,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5748,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,102 +5763,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,12 +5909,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5970,12 +5934,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5994,7 +5958,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.7</v>
+        <v>27</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5972,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
         <v>37.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,17 +5999,17 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6060,12 +6024,12 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -6092,7 +6056,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,12 +6066,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,67 +6081,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -6212,7 +6176,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6263,12 +6227,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6288,12 +6252,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6312,7 +6276,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,26 +6290,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
         <v>37.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,37 +6317,29 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -6405,12 +6361,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6420,12 +6376,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6435,67 +6391,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6530,7 +6486,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +6968,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +6992,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.2</v>
+        <v>55.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +7006,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +7019,7 @@
         <v>37.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7077,39 +7033,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7254,7 +7206,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,7 +7282,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7354,7 +7306,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50.7</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,7 +7320,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7381,7 +7333,7 @@
         <v>37.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7395,39 +7347,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7572,7 +7520,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7623,24 +7571,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -7648,7 +7596,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7658,12 +7606,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7672,7 +7620,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7686,26 +7634,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>37.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V4" t="n">
         <v>50</v>
@@ -7713,14 +7661,14 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>2</t>
@@ -7738,12 +7686,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -7765,27 +7713,27 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -7795,102 +7743,102 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7941,12 +7889,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7966,7 +7914,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8004,11 +7952,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>47.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q5" t="n">
         <v>34.3</v>
@@ -8017,13 +7965,13 @@
         <v>37.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>13.3</v>
+        <v>65.2</v>
       </c>
       <c r="V5" t="n">
         <v>50</v>
@@ -8031,39 +7979,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8083,22 +8027,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -8108,72 +8052,72 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -8208,7 +8152,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8259,12 +8203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8274,7 +8218,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8284,12 +8228,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8308,7 +8252,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8322,11 +8266,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="n">
         <v>18.6</v>
@@ -8335,31 +8279,33 @@
         <v>37.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V6" t="n">
-        <v>50</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>48</v>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8374,12 +8320,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -8401,12 +8347,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8416,82 +8362,82 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8526,7 +8472,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8560,16 +8506,56 @@
         </is>
       </c>
       <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
-      <c r="BZ6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8577,24 +8563,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -8602,7 +8588,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8612,12 +8598,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -8626,7 +8612,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8640,68 +8626,62 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>62</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>37.1</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
+        <v>80</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="V7" t="n">
         <v>50</v>
       </c>
-      <c r="U7" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>48</v>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8721,7 +8701,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -8736,117 +8716,117 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8880,56 +8860,16 @@
         </is>
       </c>
       <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8937,12 +8877,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8962,12 +8902,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8986,7 +8926,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.4</v>
+        <v>47.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,11 +8940,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
@@ -9013,13 +8953,13 @@
         <v>37.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9027,39 +8967,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9079,7 +9015,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -9089,87 +9025,87 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9204,7 +9140,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9255,12 +9191,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,12 +9216,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9304,7 +9240,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.2</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,11 +9254,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
@@ -9331,13 +9267,13 @@
         <v>37.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9345,39 +9281,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9397,7 +9329,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -9412,12 +9344,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -9427,67 +9359,67 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9522,7 +9454,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9578,7 +9510,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9598,12 +9530,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9622,7 +9554,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>43.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9568,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9581,7 @@
         <v>37.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -9663,14 +9595,14 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>6</t>
@@ -9688,12 +9620,12 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9840,7 +9772,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9896,7 +9828,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9916,7 +9848,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9872,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9886,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9899,7 @@
         <v>37.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -9981,14 +9913,14 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>1</t>
@@ -10006,12 +9938,12 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -10158,7 +10090,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10234,12 +10166,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10190,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,7 +10204,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -10285,7 +10217,7 @@
         <v>37.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -10299,14 +10231,14 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>4</t>
@@ -10324,12 +10256,12 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -10476,7 +10408,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,24 +10459,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -10552,22 +10484,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10576,7 +10508,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,26 +10522,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>37.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,17 +10549,17 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -10642,17 +10574,17 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -10669,7 +10601,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -10679,17 +10611,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,102 +10631,102 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10802,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10826,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10840,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10853,7 @@
         <v>37.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -10935,39 +10867,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11112,7 +11040,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11091,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11188,7 +11116,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11212,7 +11140,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>32.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,11 +11154,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
@@ -11239,13 +11167,13 @@
         <v>37.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11181,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,12 +11229,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,12 +11244,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,27 +11259,27 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -11365,37 +11289,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11354,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,12 +11405,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11506,12 +11430,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11530,7 +11454,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.2</v>
+        <v>32.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,11 +11468,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
@@ -11557,13 +11481,13 @@
         <v>37.1</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>70.59999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,17 +11495,17 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -11596,12 +11520,12 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -11623,27 +11547,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,67 +11577,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11748,7 +11672,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,24 +11723,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -11824,7 +11748,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11834,12 +11758,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11848,7 +11772,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.8</v>
+        <v>31.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11786,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
         <v>37.1</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,39 +11813,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11941,12 +11861,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11876,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,102 +11891,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,12 +12037,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12142,12 +12062,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12166,7 +12086,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.7</v>
+        <v>27</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12100,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
         <v>37.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,17 +12127,17 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -12232,12 +12152,12 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -12264,7 +12184,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,12 +12194,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,67 +12209,67 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -12384,7 +12304,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12435,12 +12355,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12460,12 +12380,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12484,7 +12404,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,26 +12418,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
         <v>37.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,37 +12445,29 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -12577,12 +12489,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12592,12 +12504,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12607,67 +12519,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12702,7 +12614,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>59 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1538,34 +1538,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1710,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2024,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2172,34 +2168,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2344,7 +2336,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2698,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3012,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3326,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3472,34 +3464,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3644,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3790,34 +3778,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3962,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4108,34 +4092,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4280,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4426,34 +4406,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4598,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4912,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5226,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5372,34 +5348,30 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5544,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5858,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6004,34 +5976,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6176,7 +6144,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6320,28 +6288,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6486,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7206,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7520,7 +7492,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7666,34 +7638,30 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7838,7 +7806,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8152,7 +8120,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8300,34 +8268,30 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8472,7 +8436,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8826,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -9140,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9454,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9600,34 +9564,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9772,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9918,34 +9878,30 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10090,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10236,34 +10192,30 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10408,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10554,34 +10506,30 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10726,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -11040,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11354,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11500,34 +11448,30 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11672,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11986,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12132,34 +12076,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12304,7 +12244,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12448,28 +12388,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12614,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
